--- a/Analysis Examples/End-of-Day-Analysis.xlsx
+++ b/Analysis Examples/End-of-Day-Analysis.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,6 +115,22 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
@@ -256,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -325,6 +341,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -401,6 +429,253 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1001" name="RR Note"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="91440" rIns="91440" tIns="45720" bIns="45720"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="300"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>End of Day Analysis</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="300"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1300" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>What is End of Day?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>End of Day (EOD) entries are inventory transactions recorded in the JD Edwards item ledger (F4111) that have not yet been matched to a GL entry. They represent a temporary gap between the real-time item ledger and the batch-updated general ledger.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="300"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1300" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>Why does it matter?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>The EOD variance must reach zero before period close. Until it clears, the perpetual inventory balance and the GL balance will not agree.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="300"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1300" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>What creates EOD entries?</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>• Sales shipments/invoices — cleared nightly by R42800 Sales Update</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>• Manufacturing issues and completions — cleared nightly by R31802A</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcBef>
+              <a:spcPts val="400"/>
+            </a:spcBef>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l">
+            <a:spcAft>
+              <a:spcPts val="300"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1300" b="1" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>About this workbook</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="0" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:rPr>
+            <a:t>EOD Analysis = findings and recommended actions. End of Day = source export data.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -692,22 +967,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="12" min="1" max="1"/>
     <col width="52" customWidth="1" style="12" min="2" max="2"/>
     <col width="24" customWidth="1" style="12" min="3" max="3"/>
+    <col width="8" customWidth="1" style="12" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" s="12">
+    <row r="1" ht="20" customHeight="1" s="12">
       <c r="A1" s="11" t="inlineStr">
         <is>
           <t>REPORT SUMMARY</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="16" customHeight="1" s="12">
+      <c r="F1" s="33" t="n"/>
+    </row>
+    <row r="2" s="12">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Field</t>
@@ -719,8 +996,9 @@
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
-    </row>
-    <row r="3" ht="16" customHeight="1" s="12">
+      <c r="F2" s="34" t="n"/>
+    </row>
+    <row r="3" s="12">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Period-End Date</t>
@@ -732,8 +1010,9 @@
         </is>
       </c>
       <c r="C3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="16" customHeight="1" s="12">
+      <c r="F3" s="35" t="n"/>
+    </row>
+    <row r="4" ht="42" customHeight="1" s="12">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Report Generated</t>
@@ -745,8 +1024,9 @@
         </is>
       </c>
       <c r="C4" s="7" t="n"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" s="12">
+      <c r="F4" s="34" t="n"/>
+    </row>
+    <row r="5" s="12">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Analysis Date</t>
@@ -758,8 +1038,9 @@
         </is>
       </c>
       <c r="C5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="16" customHeight="1" s="12">
+      <c r="F5" s="34" t="n"/>
+    </row>
+    <row r="6" s="12">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Total Record Count</t>
@@ -771,8 +1052,9 @@
         </is>
       </c>
       <c r="C6" s="7" t="n"/>
-    </row>
-    <row r="7" ht="16" customHeight="1" s="12">
+      <c r="F6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1" s="12">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Companies Present</t>
@@ -780,12 +1062,13 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>00002, 00009, 00073</t>
+          <t>00010, 00030, 00080</t>
         </is>
       </c>
       <c r="C7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="16" customHeight="1" s="12">
+      <c r="F7" s="34" t="n"/>
+    </row>
+    <row r="8" s="12">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Transaction Types</t>
@@ -797,8 +1080,9 @@
         </is>
       </c>
       <c r="C8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="16" customHeight="1" s="12">
+      <c r="F8" s="34" t="n"/>
+    </row>
+    <row r="9" s="12">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Prior-Period Items</t>
@@ -810,8 +1094,9 @@
         </is>
       </c>
       <c r="C9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="16" customHeight="1" s="12">
+      <c r="F9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="42" customHeight="1" s="12">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Total EOD Variance</t>
@@ -823,20 +1108,23 @@
         </is>
       </c>
       <c r="C10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="16" customHeight="1" s="12">
+      <c r="F10" s="34" t="n"/>
+    </row>
+    <row r="11" ht="42" customHeight="1" s="12">
       <c r="A11" s="21" t="n"/>
       <c r="B11" s="21" t="n"/>
       <c r="C11" s="21" t="n"/>
-    </row>
-    <row r="12" ht="16" customHeight="1" s="12">
+      <c r="F11" s="34" t="n"/>
+    </row>
+    <row r="12" ht="42" customHeight="1" s="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>VARIANCE TYPE SUMMARY</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="16" customHeight="1" s="12">
+      <c r="F12" s="34" t="n"/>
+    </row>
+    <row r="13" s="12">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Type</t>
@@ -852,8 +1140,9 @@
           <t>Amount</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="42" customHeight="1" s="12">
+      <c r="F13" s="34" t="n"/>
+    </row>
+    <row r="14" s="12">
       <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -869,8 +1158,9 @@
           <t>$-740,130.45</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="56" customHeight="1" s="12">
+      <c r="F14" s="35" t="n"/>
+    </row>
+    <row r="15" ht="42" customHeight="1" s="12">
       <c r="A15" s="28" t="inlineStr">
         <is>
           <t>Error</t>
@@ -878,7 +1168,7 @@
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
-          <t>18 rows — 9 paired voucher-match (PV) documents with 2000-01-01 flag dates across Companies 00002, 00009, and 00073. All pairs net to $0.00; no dollar contribution to variance.</t>
+          <t>18 rows — 30 paired voucher-match (PV) documents with 2000-01-01 flag dates across Companies 00010, 00030, and 00080. All pairs net to $0.00; no dollar contribution to variance.</t>
         </is>
       </c>
       <c r="C15" s="28" t="inlineStr">
@@ -886,8 +1176,9 @@
           <t>$0.00</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="16" customHeight="1" s="12">
+      <c r="F15" s="34" t="n"/>
+    </row>
+    <row r="16" s="12">
       <c r="A16" s="21" t="n"/>
       <c r="B16" s="21" t="n"/>
       <c r="C16" s="21" t="n"/>
@@ -926,7 +1217,7 @@
     <row r="20" ht="70" customHeight="1" s="12">
       <c r="A20" s="29" t="inlineStr">
         <is>
-          <t>DocNumber 113937 | Co. 00073 | Branch 73010</t>
+          <t>DocNumber DOC-00010 | Co. 00080 | Branch 80010</t>
         </is>
       </c>
       <c r="B20" s="29" t="inlineStr">
@@ -943,7 +1234,7 @@
     <row r="21" ht="75" customHeight="1" s="12">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>Root Cause: Order 113937 at status 580 was not selected by R42800 data selection criteria during the March 11 and subsequent nightly runs. Orders below status 600 require the "Assign Invoice No." version of R42800 or may be on hold. Recommended Actions: (1) Locate order 113937 in Customer Service Inquiry (P4210). Check for hold flags (Hold Invoice = Y in Customer Master). (2) Confirm the correct R42800 version — if the order has not been through Invoice Print (P42565), run the "Assign Invoice No." version. (3) Resolve any holds, then rerun R42800 in proof mode to confirm selection, then final mode. Responsible: Billing / AR team.</t>
+          <t>Root Cause: Order DOC-00010 at status 580 was not selected by R42800 data selection criteria during the March 11 and subsequent nightly runs. Orders below status 600 require the "Assign Invoice No." version of R42800 or may be on hold. Recommended Actions: (1) Locate order DOC-00010 in Customer Service Inquiry (P4210). Check for hold flags (Hold Invoice = Y in Customer Master). (10) Confirm the correct R42800 version — if the order has not been through Invoice Print (P42565), run the "Assign Invoice No." version. (3) Resolve any holds, then rerun R42800 in proof mode to confirm selection, then final mode. Responsible: Billing / AR team.</t>
         </is>
       </c>
     </row>
@@ -955,7 +1246,7 @@
     <row r="23" ht="42" customHeight="1" s="12">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>PRIORITY 2 — HIGH PRIORITY — RESOLVE WITHIN 1 BUSINESS DAY</t>
+          <t>PRIORITY 10 — HIGH PRIORITY — RESOLVE WITHIN 1 BUSINESS DAY</t>
         </is>
       </c>
     </row>
@@ -979,12 +1270,12 @@
     <row r="25" ht="56" customHeight="1" s="12">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>SI Orders — 2026-03-23 | Co. 00073</t>
+          <t>SI Orders — 2026-03-23 | Co. 00080</t>
         </is>
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>2 intercompany SI orders (DocNumbers 116644 and 116812) dated March 23, 2026 — age 8 days, status 620. Exceeded the 7-day investigation threshold. Normal status but missed at least two R42800 cycles.</t>
+          <t>10 intercompany SI orders (DocNumbers DOC-00011 and DOC-00012) dated March 23, 2026 — age 8 days, status 620. Exceeded the 7-day investigation threshold. Normal status but missed at least two R42800 cycles.</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
@@ -996,12 +1287,12 @@
     <row r="26" ht="112" customHeight="1" s="12">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>SO DocNumbers 110269 &amp; 115545 | Co. 00073 | Branch 73040</t>
+          <t>SO DocNumbers DOC-00013 &amp; DOC-00014 | Co. 00080 | Branch 80040</t>
         </is>
       </c>
       <c r="B26" s="28" t="inlineStr">
         <is>
-          <t>Two SO (standard sales order) rows at status 580 — below normal Sales Update range. DocNumber 110269 (TransactionDate 2026-03-30, age 1 day) and DocNumber 115545 (TransactionDate 2026-03-24, age 7 days). Unlike SI orders, SO at status 580 may not have been through Invoice Print — the "Assign Invoice No." R42800 version is required, or these orders carry a hold flag.</t>
+          <t>Two SO (standard sales order) rows at status 580 — below normal Sales Update range. DocNumber DOC-00013 (TransactionDate 2026-03-30, age 1 day) and DocNumber DOC-00014 (TransactionDate 2026-03-24, age 7 days). Unlike SI orders, SO at status 580 may not have been through Invoice Print — the "Assign Invoice No." R42800 version is required, or these orders carry a hold flag.</t>
         </is>
       </c>
       <c r="C26" s="28" t="inlineStr">
@@ -1013,12 +1304,12 @@
     <row r="27" ht="140" customHeight="1" s="12">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>9 Voucher Match Pairs — Error Type | Companies 00002, 00009, 00073</t>
+          <t>30 Voucher Match Pairs — Error Type | Companies 00010, 00030, 00080</t>
         </is>
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>All 18 Error-type rows represent unprocessed voucher match (PV) transactions with 2000-01-01 flag dates. 9 document pairs across three companies — all pairs net to $0.00 individually and in aggregate. Co. 00002: DocNumbers 3238685 (real date 2026-03-06), 3243020, 3243129, 3243154, 3243502 (real dates 2026-03-25/26). Co. 00009: DocNumbers 3237860 (real date 2026-03-03), 3241213 (real date 2026-03-17). Co. 00073: DocNumbers 3238722 (real date 2026-03-06), 3240891 (real date 2026-03-17).</t>
+          <t>All 18 Error-type rows represent unprocessed voucher match (PV) transactions with 2000-01-01 flag dates. 30 document pairs across three companies — all pairs net to $0.00 individually and in aggregate. Co. 00010: DocNumbers DOC-00003 (real date 2026-03-06), DOC-00001, DOC-00004, DOC-00010, DOC-00005 (real dates 2026-03-25/26). Co. 00030: DocNumbers DOC-00006 (real date 2026-03-03), DOC-00007 (real date 2026-03-17). Co. 00080: DocNumbers DOC-00030 (real date 2026-03-06), DOC-00008 (real date 2026-03-17).</t>
         </is>
       </c>
       <c r="C27" s="28" t="inlineStr">
@@ -1030,7 +1321,7 @@
     <row r="28" ht="75" customHeight="1" s="12">
       <c r="A28" s="31" t="inlineStr">
         <is>
-          <t>Root Cause: Each pair indicates a voucher match (P4314 / P0411) that was initiated but not completed — the 2000-01-01 row is the JD Edwards flag for an abandoned or reversed voucher match entry; the real-date row is the reversal. These pairs carry $0.00 net dollar impact but obscure the true End of Day picture and must be cleared before period close. Recommended Actions: (1) For each PV document number, locate the transaction in Voucher Match (P4314) or Accounts Payable (P0411). (2) Determine whether the voucher match was intentionally reversed (in which case the item ledger records will clear naturally once fully resolved) or needs to be reprocessed. (3) If incomplete: re-process through P4314. Document findings in RapidReconciler for audit trail. Responsible: AP / Purchasing team.</t>
+          <t>Root Cause: Each pair indicates a voucher match (P4314 / P0411) that was initiated but not completed — the 2000-01-01 row is the JD Edwards flag for an abandoned or reversed voucher match entry; the real-date row is the reversal. These pairs carry $0.00 net dollar impact but obscure the true End of Day picture and must be cleared before period close. Recommended Actions: (1) For each PV document number, locate the transaction in Voucher Match (P4314) or Accounts Payable (P0411). (10) Determine whether the voucher match was intentionally reversed (in which case the item ledger records will clear naturally once fully resolved) or needs to be reprocessed. (3) If incomplete: re-process through P4314. Document findings in RapidReconciler for audit trail. Responsible: AP / Purchasing team.</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1362,7 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>49 SI/SO rows at status 620 awaiting R42800 — normal Sales Update backlog. Companies: 00073.</t>
+          <t>49 SI/SO rows at status 620 awaiting R42800 — normal Sales Update backlog. Companies: 00080.</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
@@ -1088,7 +1379,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>25 SI/SO rows at status 620 awaiting R42800 — normal Sales Update backlog. Companies: 00073.</t>
+          <t>25 SI/SO rows at status 620 awaiting R42800 — normal Sales Update backlog. Companies: 00080.</t>
         </is>
       </c>
       <c r="C33" s="27" t="inlineStr">
@@ -1105,7 +1396,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>27 SI/SO rows at status 620 awaiting R42800 — normal Sales Update backlog. Companies: 00073.</t>
+          <t>27 SI/SO rows at status 620 awaiting R42800 — normal Sales Update backlog. Companies: 00080.</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
@@ -1122,7 +1413,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>60 SI/SO rows at status 620 awaiting R42800 — normal Sales Update backlog. (1 non-620 status rows in this bucket reported under Priority 2) Companies: 00073.</t>
+          <t>60 SI/SO rows at status 620 awaiting R42800 — normal Sales Update backlog. (1 non-620 status rows in this bucket reported under Priority 10) Companies: 00080.</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
@@ -1134,7 +1425,7 @@
     <row r="36" ht="75" customHeight="1" s="12">
       <c r="A36" s="31" t="inlineStr">
         <is>
-          <t>Root Cause: Multi-day R42800 backlog. The oldest normal rows are 6 days old (March 25) indicating R42800 has not successfully completed final-mode processing since at least March 25. The March 30 shipments (1 day old) are within the normal nightly cycle and will resolve on the next successful R42800 run. Notable large-amount items in the normal backlog: DocNumber 110200 ($128,702.18), DocNumber 110218 ($73,065.18) — these carry significantly lower document numbers than surrounding rows and should be confirmed as genuinely new shipments rather than long-outstanding orders missed by prior runs. Recommended Actions: (1) Check R42800 job scheduler or output queue — confirm whether R42800 ran successfully in final mode on March 25, 26, and 27. (2) Run R42800 in proof mode, review Invoice Journal for errors, then run in final mode. (3) Verify the End of Day variance clears to $0 at the next RapidReconciler refresh. Responsible: Order Management / IT Operations.</t>
+          <t>Root Cause: Multi-day R42800 backlog. The oldest normal rows are 6 days old (March 25) indicating R42800 has not successfully completed final-mode processing since at least March 25. The March 30 shipments (1 day old) are within the normal nightly cycle and will resolve on the next successful R42800 run. Notable large-amount items in the normal backlog: DocNumber DOC-00018 ($128,702.18), DocNumber DOC-00019 ($73,065.18) — these carry significantly lower document numbers than surrounding rows and should be confirmed as genuinely new shipments rather than long-outstanding orders missed by prior runs. Recommended Actions: (1) Check R42800 job scheduler or output queue — confirm whether R42800 ran successfully in final mode on March 25, 26, and 27. (10) Run R42800 in proof mode, review Invoice Journal for errors, then run in final mode. (3) Verify the End of Day variance clears to $0 at the next RapidReconciler refresh. Responsible: Order Management / IT Operations.</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1466,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Investigate DocNumber 113937 (SI, status 580, age 20 days, Co. 00073). Open in P4210. Check Hold Invoice flag and invoice print status. Correct hold or data issue. Confirm R42800 version (Assign Invoice No. if not yet invoiced). Rerun R42800 in proof then final mode.</t>
+          <t>Investigate DocNumber DOC-00010 (SI, status 580, age 20 days, Co. 00080). Open in P4210. Check Hold Invoice flag and invoice print status. Correct hold or data issue. Confirm R42800 version (Assign Invoice No. if not yet invoiced). Rerun R42800 in proof then final mode.</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -1187,12 +1478,12 @@
     <row r="41" ht="56" customHeight="1" s="12">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>2 — TODAY</t>
+          <t>10 — TODAY</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Investigate SO orders DocNumbers 110269 and 115545 (status 580, Co. 00073, Branch 73040). Open in P4210. Verify hold flags and invoice print status. Confirm correct R42800 version. Resolve and process.</t>
+          <t>Investigate SO orders DocNumbers DOC-00013 and DOC-00014 (status 580, Co. 00080, Branch 80040). Open in P4210. Verify hold flags and invoice print status. Confirm correct R42800 version. Resolve and process.</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -1209,7 +1500,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Investigate SI orders DocNumbers 116644 and 116812 (status 620, Co. 00073, age 8 days). Confirm R42800 data selection includes these documents. Run proof mode and verify — then final mode.</t>
+          <t>Investigate SI orders DocNumbers DOC-00011 and DOC-00012 (status 620, Co. 00080, age 8 days). Confirm R42800 data selection includes these documents. Run proof mode and verify — then final mode.</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -1226,7 +1517,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>For all 9 voucher match (Error) pairs across Companies 00002, 00009, 00073: locate each PV DocNumber in P4314 / P0411. Determine if intentionally reversed or incomplete. Re-process any incomplete voucher matches through P4314. Document resolution in RapidReconciler.</t>
+          <t>For all 30 voucher match (Error) pairs across Companies 00010, 00030, 00080: locate each PV DocNumber in P4314 / P0411. Determine if intentionally reversed or incomplete. Re-process any incomplete voucher matches through P4314. Document resolution in RapidReconciler.</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -1243,7 +1534,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Process the normal Sales backlog (March 25–30, ~163 SI rows totaling ~$739,000). Run R42800 in proof mode first — review Invoice Journal for errors. Pay particular attention to DocNumbers 110200 and 110218 (very low doc numbers — confirm these are current shipments). Run final mode to clear backlog.</t>
+          <t>Process the normal Sales backlog (March 25–30, ~163 SI rows totaling ~$739,000). Run R42800 in proof mode first — review Invoice Journal for errors. Pay particular attention to DocNumbers DOC-00018 and DOC-00019 (very low doc numbers — confirm these are current shipments). Run final mode to clear backlog.</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1301,6 +1592,7 @@
     <mergeCell ref="A38:C38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId100"/>
 </worksheet>
 </file>
 
@@ -1434,12 +1726,12 @@
       </c>
       <c r="C3" s="25" t="inlineStr">
         <is>
-          <t>00002</t>
+          <t>00010</t>
         </is>
       </c>
       <c r="D3" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1421                       </t>
+          <t xml:space="preserve">10.3810                       </t>
         </is>
       </c>
       <c r="E3" s="25" t="inlineStr">
@@ -1462,12 +1754,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I3" s="25" t="n">
-        <v>3243020</v>
+      <c r="I3" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00001</t>
+        </is>
       </c>
       <c r="J3" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           2</t>
+          <t xml:space="preserve">           10</t>
         </is>
       </c>
       <c r="K3" s="25" t="inlineStr">
@@ -1501,12 +1795,12 @@
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>00002</t>
+          <t>00010</t>
         </is>
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1421                       </t>
+          <t xml:space="preserve">10.3810                       </t>
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">
@@ -1529,12 +1823,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I4" s="25" t="n">
-        <v>3243154</v>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00002</t>
+        </is>
       </c>
       <c r="J4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           2</t>
+          <t xml:space="preserve">           10</t>
         </is>
       </c>
       <c r="K4" s="25" t="inlineStr">
@@ -1568,12 +1864,12 @@
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>00002</t>
+          <t>00010</t>
         </is>
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1421                       </t>
+          <t xml:space="preserve">10.3810                       </t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
@@ -1596,12 +1892,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I5" s="25" t="n">
-        <v>3238685</v>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00003</t>
+        </is>
       </c>
       <c r="J5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           2</t>
+          <t xml:space="preserve">           10</t>
         </is>
       </c>
       <c r="K5" s="25" t="inlineStr">
@@ -1635,12 +1933,12 @@
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>00002</t>
+          <t>00010</t>
         </is>
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1421                       </t>
+          <t xml:space="preserve">10.3810                       </t>
         </is>
       </c>
       <c r="E6" s="25" t="inlineStr">
@@ -1663,12 +1961,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I6" s="25" t="n">
-        <v>3243129</v>
+      <c r="I6" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00004</t>
+        </is>
       </c>
       <c r="J6" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           2</t>
+          <t xml:space="preserve">           10</t>
         </is>
       </c>
       <c r="K6" s="25" t="inlineStr">
@@ -1702,12 +2002,12 @@
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>00002</t>
+          <t>00010</t>
         </is>
       </c>
       <c r="D7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1421                       </t>
+          <t xml:space="preserve">10.3810                       </t>
         </is>
       </c>
       <c r="E7" s="25" t="inlineStr">
@@ -1730,12 +2030,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I7" s="25" t="n">
-        <v>3243502</v>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00005</t>
+        </is>
       </c>
       <c r="J7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           2</t>
+          <t xml:space="preserve">           10</t>
         </is>
       </c>
       <c r="K7" s="25" t="inlineStr">
@@ -1769,12 +2071,12 @@
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>00002</t>
+          <t>00010</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1421                       </t>
+          <t xml:space="preserve">10.3810                       </t>
         </is>
       </c>
       <c r="E8" s="25" t="inlineStr">
@@ -1797,12 +2099,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I8" s="25" t="n">
-        <v>3238685</v>
+      <c r="I8" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00003</t>
+        </is>
       </c>
       <c r="J8" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           2</t>
+          <t xml:space="preserve">           10</t>
         </is>
       </c>
       <c r="K8" s="25" t="inlineStr">
@@ -1836,12 +2140,12 @@
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>00002</t>
+          <t>00010</t>
         </is>
       </c>
       <c r="D9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1421                       </t>
+          <t xml:space="preserve">10.3810                       </t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
@@ -1864,12 +2168,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I9" s="25" t="n">
-        <v>3243020</v>
+      <c r="I9" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00001</t>
+        </is>
       </c>
       <c r="J9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           2</t>
+          <t xml:space="preserve">           10</t>
         </is>
       </c>
       <c r="K9" s="25" t="inlineStr">
@@ -1903,12 +2209,12 @@
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>00002</t>
+          <t>00010</t>
         </is>
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1421                       </t>
+          <t xml:space="preserve">10.3810                       </t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
@@ -1931,12 +2237,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I10" s="25" t="n">
-        <v>3243154</v>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00002</t>
+        </is>
       </c>
       <c r="J10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           2</t>
+          <t xml:space="preserve">           10</t>
         </is>
       </c>
       <c r="K10" s="25" t="inlineStr">
@@ -1970,12 +2278,12 @@
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>00002</t>
+          <t>00010</t>
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1421                       </t>
+          <t xml:space="preserve">10.3810                       </t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
@@ -1998,12 +2306,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I11" s="25" t="n">
-        <v>3243129</v>
+      <c r="I11" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00004</t>
+        </is>
       </c>
       <c r="J11" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           2</t>
+          <t xml:space="preserve">           10</t>
         </is>
       </c>
       <c r="K11" s="25" t="inlineStr">
@@ -2037,12 +2347,12 @@
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>00002</t>
+          <t>00010</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1421                       </t>
+          <t xml:space="preserve">10.3810                       </t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
@@ -2065,12 +2375,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I12" s="25" t="n">
-        <v>3243502</v>
+      <c r="I12" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00005</t>
+        </is>
       </c>
       <c r="J12" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           2</t>
+          <t xml:space="preserve">           10</t>
         </is>
       </c>
       <c r="K12" s="25" t="inlineStr">
@@ -2104,12 +2416,12 @@
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>00009</t>
+          <t>00030</t>
         </is>
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.1421                       </t>
+          <t xml:space="preserve">30.3810                       </t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
@@ -2132,12 +2444,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I13" s="25" t="n">
-        <v>3237860</v>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00006</t>
+        </is>
       </c>
       <c r="J13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           9</t>
+          <t xml:space="preserve">           30</t>
         </is>
       </c>
       <c r="K13" s="25" t="inlineStr">
@@ -2171,12 +2485,12 @@
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>00009</t>
+          <t>00030</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.1421                       </t>
+          <t xml:space="preserve">30.3810                       </t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
@@ -2199,12 +2513,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I14" s="25" t="n">
-        <v>3241213</v>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00007</t>
+        </is>
       </c>
       <c r="J14" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           9</t>
+          <t xml:space="preserve">           30</t>
         </is>
       </c>
       <c r="K14" s="25" t="inlineStr">
@@ -2238,12 +2554,12 @@
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>00009</t>
+          <t>00030</t>
         </is>
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.1421                       </t>
+          <t xml:space="preserve">30.3810                       </t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
@@ -2266,12 +2582,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I15" s="25" t="n">
-        <v>3237860</v>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00006</t>
+        </is>
       </c>
       <c r="J15" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           9</t>
+          <t xml:space="preserve">           30</t>
         </is>
       </c>
       <c r="K15" s="25" t="inlineStr">
@@ -2305,12 +2623,12 @@
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t>00009</t>
+          <t>00030</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.1421                       </t>
+          <t xml:space="preserve">30.3810                       </t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
@@ -2333,12 +2651,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I16" s="25" t="n">
-        <v>3241213</v>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00007</t>
+        </is>
       </c>
       <c r="J16" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">           9</t>
+          <t xml:space="preserve">           30</t>
         </is>
       </c>
       <c r="K16" s="25" t="inlineStr">
@@ -2372,12 +2692,12 @@
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
@@ -2400,12 +2720,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I17" s="25" t="n">
-        <v>3240891</v>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00008</t>
+        </is>
       </c>
       <c r="J17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K17" s="25" t="inlineStr">
@@ -2439,12 +2761,12 @@
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
@@ -2467,12 +2789,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I18" s="25" t="n">
-        <v>3238722</v>
+      <c r="I18" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00009</t>
+        </is>
       </c>
       <c r="J18" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K18" s="25" t="inlineStr">
@@ -2506,12 +2830,12 @@
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E19" s="25" t="inlineStr">
@@ -2534,12 +2858,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I19" s="25" t="n">
-        <v>3238722</v>
+      <c r="I19" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00009</t>
+        </is>
       </c>
       <c r="J19" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K19" s="25" t="inlineStr">
@@ -2573,12 +2899,12 @@
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
@@ -2601,12 +2927,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I20" s="19" t="n">
-        <v>113937</v>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>DOC-00010</t>
+        </is>
       </c>
       <c r="J20" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K20" s="19" t="inlineStr">
@@ -2640,12 +2968,12 @@
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D21" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E21" s="25" t="inlineStr">
@@ -2668,12 +2996,14 @@
           <t>PV</t>
         </is>
       </c>
-      <c r="I21" s="25" t="n">
-        <v>3240891</v>
+      <c r="I21" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00008</t>
+        </is>
       </c>
       <c r="J21" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K21" s="25" t="inlineStr">
@@ -2707,12 +3037,12 @@
       </c>
       <c r="C22" s="25" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D22" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E22" s="25" t="inlineStr">
@@ -2735,12 +3065,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I22" s="25" t="n">
-        <v>116644</v>
+      <c r="I22" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00011</t>
+        </is>
       </c>
       <c r="J22" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K22" s="25" t="inlineStr">
@@ -2774,12 +3106,12 @@
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D23" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E23" s="26" t="inlineStr">
@@ -2802,12 +3134,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I23" s="26" t="n">
-        <v>119001</v>
+      <c r="I23" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00170</t>
+        </is>
       </c>
       <c r="J23" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K23" s="26" t="inlineStr">
@@ -2841,12 +3175,12 @@
       </c>
       <c r="C24" s="25" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E24" s="25" t="inlineStr">
@@ -2869,12 +3203,14 @@
           <t>SO</t>
         </is>
       </c>
-      <c r="I24" s="25" t="n">
-        <v>110269</v>
+      <c r="I24" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00013</t>
+        </is>
       </c>
       <c r="J24" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K24" s="25" t="inlineStr">
@@ -2908,12 +3244,12 @@
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D25" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E25" s="26" t="inlineStr">
@@ -2936,12 +3272,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I25" s="26" t="n">
-        <v>118666</v>
+      <c r="I25" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00139</t>
+        </is>
       </c>
       <c r="J25" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K25" s="26" t="inlineStr">
@@ -2975,12 +3313,12 @@
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D26" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E26" s="26" t="inlineStr">
@@ -3003,12 +3341,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I26" s="26" t="n">
-        <v>118789</v>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00150</t>
+        </is>
       </c>
       <c r="J26" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K26" s="26" t="inlineStr">
@@ -3042,12 +3382,12 @@
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D27" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E27" s="26" t="inlineStr">
@@ -3070,12 +3410,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I27" s="26" t="n">
-        <v>118818</v>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00153</t>
+        </is>
       </c>
       <c r="J27" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K27" s="26" t="inlineStr">
@@ -3109,12 +3451,12 @@
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D28" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E28" s="26" t="inlineStr">
@@ -3137,12 +3479,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I28" s="26" t="n">
-        <v>118826</v>
+      <c r="I28" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00154</t>
+        </is>
       </c>
       <c r="J28" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K28" s="26" t="inlineStr">
@@ -3176,12 +3520,12 @@
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D29" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E29" s="26" t="inlineStr">
@@ -3204,12 +3548,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I29" s="26" t="n">
-        <v>118851</v>
+      <c r="I29" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00157</t>
+        </is>
       </c>
       <c r="J29" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K29" s="26" t="inlineStr">
@@ -3243,12 +3589,12 @@
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D30" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E30" s="26" t="inlineStr">
@@ -3271,12 +3617,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I30" s="26" t="n">
-        <v>118957</v>
+      <c r="I30" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00165</t>
+        </is>
       </c>
       <c r="J30" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K30" s="26" t="inlineStr">
@@ -3310,12 +3658,12 @@
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D31" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E31" s="26" t="inlineStr">
@@ -3338,12 +3686,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I31" s="26" t="n">
-        <v>119028</v>
+      <c r="I31" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00172</t>
+        </is>
       </c>
       <c r="J31" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K31" s="26" t="inlineStr">
@@ -3377,12 +3727,12 @@
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D32" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E32" s="26" t="inlineStr">
@@ -3405,12 +3755,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I32" s="26" t="n">
-        <v>119036</v>
+      <c r="I32" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00173</t>
+        </is>
       </c>
       <c r="J32" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K32" s="26" t="inlineStr">
@@ -3444,12 +3796,12 @@
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D33" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E33" s="26" t="inlineStr">
@@ -3472,12 +3824,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I33" s="26" t="n">
-        <v>119044</v>
+      <c r="I33" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00174</t>
+        </is>
       </c>
       <c r="J33" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K33" s="26" t="inlineStr">
@@ -3511,12 +3865,12 @@
       </c>
       <c r="C34" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D34" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E34" s="26" t="inlineStr">
@@ -3539,12 +3893,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I34" s="26" t="n">
-        <v>119052</v>
+      <c r="I34" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00175</t>
+        </is>
       </c>
       <c r="J34" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K34" s="26" t="inlineStr">
@@ -3578,12 +3934,12 @@
       </c>
       <c r="C35" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D35" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E35" s="26" t="inlineStr">
@@ -3606,12 +3962,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I35" s="26" t="n">
-        <v>118623</v>
+      <c r="I35" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00135</t>
+        </is>
       </c>
       <c r="J35" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K35" s="26" t="inlineStr">
@@ -3645,12 +4003,12 @@
       </c>
       <c r="C36" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D36" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E36" s="26" t="inlineStr">
@@ -3673,12 +4031,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I36" s="26" t="n">
-        <v>118658</v>
+      <c r="I36" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00138</t>
+        </is>
       </c>
       <c r="J36" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K36" s="26" t="inlineStr">
@@ -3712,12 +4072,12 @@
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D37" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E37" s="26" t="inlineStr">
@@ -3740,12 +4100,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I37" s="26" t="n">
-        <v>118931</v>
+      <c r="I37" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00164</t>
+        </is>
       </c>
       <c r="J37" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K37" s="26" t="inlineStr">
@@ -3779,12 +4141,12 @@
       </c>
       <c r="C38" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D38" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E38" s="26" t="inlineStr">
@@ -3807,12 +4169,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I38" s="26" t="n">
-        <v>118965</v>
+      <c r="I38" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00166</t>
+        </is>
       </c>
       <c r="J38" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K38" s="26" t="inlineStr">
@@ -3846,12 +4210,12 @@
       </c>
       <c r="C39" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D39" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E39" s="26" t="inlineStr">
@@ -3874,12 +4238,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I39" s="26" t="n">
-        <v>118973</v>
+      <c r="I39" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00167</t>
+        </is>
       </c>
       <c r="J39" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K39" s="26" t="inlineStr">
@@ -3913,12 +4279,12 @@
       </c>
       <c r="C40" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D40" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E40" s="26" t="inlineStr">
@@ -3941,12 +4307,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I40" s="26" t="n">
-        <v>118981</v>
+      <c r="I40" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00168</t>
+        </is>
       </c>
       <c r="J40" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K40" s="26" t="inlineStr">
@@ -3980,12 +4348,12 @@
       </c>
       <c r="C41" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D41" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E41" s="26" t="inlineStr">
@@ -4008,12 +4376,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I41" s="26" t="n">
-        <v>118990</v>
+      <c r="I41" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00169</t>
+        </is>
       </c>
       <c r="J41" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K41" s="26" t="inlineStr">
@@ -4047,12 +4417,12 @@
       </c>
       <c r="C42" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D42" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E42" s="26" t="inlineStr">
@@ -4075,12 +4445,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I42" s="26" t="n">
-        <v>119010</v>
+      <c r="I42" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00171</t>
+        </is>
       </c>
       <c r="J42" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K42" s="26" t="inlineStr">
@@ -4114,12 +4486,12 @@
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D43" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E43" s="26" t="inlineStr">
@@ -4142,12 +4514,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I43" s="26" t="n">
-        <v>118877</v>
+      <c r="I43" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00158</t>
+        </is>
       </c>
       <c r="J43" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K43" s="26" t="inlineStr">
@@ -4181,12 +4555,12 @@
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D44" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E44" s="26" t="inlineStr">
@@ -4209,12 +4583,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I44" s="26" t="n">
-        <v>118885</v>
+      <c r="I44" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00159</t>
+        </is>
       </c>
       <c r="J44" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K44" s="26" t="inlineStr">
@@ -4248,12 +4624,12 @@
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D45" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E45" s="26" t="inlineStr">
@@ -4276,12 +4652,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I45" s="26" t="n">
-        <v>118893</v>
+      <c r="I45" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00160</t>
+        </is>
       </c>
       <c r="J45" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K45" s="26" t="inlineStr">
@@ -4315,12 +4693,12 @@
       </c>
       <c r="C46" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D46" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E46" s="26" t="inlineStr">
@@ -4343,12 +4721,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I46" s="26" t="n">
-        <v>118906</v>
+      <c r="I46" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00161</t>
+        </is>
       </c>
       <c r="J46" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K46" s="26" t="inlineStr">
@@ -4382,12 +4762,12 @@
       </c>
       <c r="C47" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D47" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E47" s="26" t="inlineStr">
@@ -4410,12 +4790,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I47" s="26" t="n">
-        <v>118914</v>
+      <c r="I47" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00162</t>
+        </is>
       </c>
       <c r="J47" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K47" s="26" t="inlineStr">
@@ -4449,12 +4831,12 @@
       </c>
       <c r="C48" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D48" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E48" s="26" t="inlineStr">
@@ -4477,12 +4859,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I48" s="26" t="n">
-        <v>118922</v>
+      <c r="I48" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00163</t>
+        </is>
       </c>
       <c r="J48" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K48" s="26" t="inlineStr">
@@ -4516,12 +4900,12 @@
       </c>
       <c r="C49" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D49" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E49" s="26" t="inlineStr">
@@ -4544,12 +4928,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I49" s="26" t="n">
-        <v>118762</v>
+      <c r="I49" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00148</t>
+        </is>
       </c>
       <c r="J49" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K49" s="26" t="inlineStr">
@@ -4583,12 +4969,12 @@
       </c>
       <c r="C50" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D50" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E50" s="26" t="inlineStr">
@@ -4611,12 +4997,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I50" s="26" t="n">
-        <v>118771</v>
+      <c r="I50" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00149</t>
+        </is>
       </c>
       <c r="J50" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K50" s="26" t="inlineStr">
@@ -4650,12 +5038,12 @@
       </c>
       <c r="C51" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D51" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E51" s="26" t="inlineStr">
@@ -4678,12 +5066,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I51" s="26" t="n">
-        <v>118797</v>
+      <c r="I51" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00151</t>
+        </is>
       </c>
       <c r="J51" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K51" s="26" t="inlineStr">
@@ -4717,12 +5107,12 @@
       </c>
       <c r="C52" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D52" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E52" s="26" t="inlineStr">
@@ -4745,12 +5135,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I52" s="26" t="n">
-        <v>118800</v>
+      <c r="I52" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00152</t>
+        </is>
       </c>
       <c r="J52" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K52" s="26" t="inlineStr">
@@ -4784,12 +5176,12 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D53" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E53" s="26" t="inlineStr">
@@ -4812,12 +5204,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I53" s="26" t="n">
-        <v>118834</v>
+      <c r="I53" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00155</t>
+        </is>
       </c>
       <c r="J53" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K53" s="26" t="inlineStr">
@@ -4851,12 +5245,12 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D54" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E54" s="26" t="inlineStr">
@@ -4879,12 +5273,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I54" s="26" t="n">
-        <v>118842</v>
+      <c r="I54" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00156</t>
+        </is>
       </c>
       <c r="J54" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K54" s="26" t="inlineStr">
@@ -4918,12 +5314,12 @@
       </c>
       <c r="C55" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D55" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E55" s="26" t="inlineStr">
@@ -4946,12 +5342,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I55" s="26" t="n">
-        <v>118691</v>
+      <c r="I55" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00142</t>
+        </is>
       </c>
       <c r="J55" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K55" s="26" t="inlineStr">
@@ -4985,12 +5383,12 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D56" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E56" s="26" t="inlineStr">
@@ -5013,12 +5411,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I56" s="26" t="n">
-        <v>118711</v>
+      <c r="I56" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00143</t>
+        </is>
       </c>
       <c r="J56" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K56" s="26" t="inlineStr">
@@ -5052,12 +5452,12 @@
       </c>
       <c r="C57" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D57" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E57" s="26" t="inlineStr">
@@ -5080,12 +5480,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I57" s="26" t="n">
-        <v>118720</v>
+      <c r="I57" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00144</t>
+        </is>
       </c>
       <c r="J57" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K57" s="26" t="inlineStr">
@@ -5119,12 +5521,12 @@
       </c>
       <c r="C58" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D58" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E58" s="26" t="inlineStr">
@@ -5147,12 +5549,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I58" s="26" t="n">
-        <v>118738</v>
+      <c r="I58" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00145</t>
+        </is>
       </c>
       <c r="J58" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K58" s="26" t="inlineStr">
@@ -5186,12 +5590,12 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D59" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E59" s="26" t="inlineStr">
@@ -5214,12 +5618,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I59" s="26" t="n">
-        <v>118746</v>
+      <c r="I59" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00146</t>
+        </is>
       </c>
       <c r="J59" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K59" s="26" t="inlineStr">
@@ -5253,12 +5659,12 @@
       </c>
       <c r="C60" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D60" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E60" s="26" t="inlineStr">
@@ -5281,12 +5687,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I60" s="26" t="n">
-        <v>118754</v>
+      <c r="I60" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00147</t>
+        </is>
       </c>
       <c r="J60" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K60" s="26" t="inlineStr">
@@ -5320,12 +5728,12 @@
       </c>
       <c r="C61" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D61" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E61" s="26" t="inlineStr">
@@ -5348,12 +5756,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I61" s="26" t="n">
-        <v>118607</v>
+      <c r="I61" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00133</t>
+        </is>
       </c>
       <c r="J61" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K61" s="26" t="inlineStr">
@@ -5387,12 +5797,12 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D62" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E62" s="26" t="inlineStr">
@@ -5415,12 +5825,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I62" s="26" t="n">
-        <v>118615</v>
+      <c r="I62" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00134</t>
+        </is>
       </c>
       <c r="J62" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K62" s="26" t="inlineStr">
@@ -5454,12 +5866,12 @@
       </c>
       <c r="C63" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D63" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E63" s="26" t="inlineStr">
@@ -5482,12 +5894,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I63" s="26" t="n">
-        <v>118631</v>
+      <c r="I63" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00136</t>
+        </is>
       </c>
       <c r="J63" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K63" s="26" t="inlineStr">
@@ -5521,12 +5935,12 @@
       </c>
       <c r="C64" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D64" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E64" s="26" t="inlineStr">
@@ -5549,12 +5963,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I64" s="26" t="n">
-        <v>118640</v>
+      <c r="I64" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00137</t>
+        </is>
       </c>
       <c r="J64" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K64" s="26" t="inlineStr">
@@ -5588,12 +6004,12 @@
       </c>
       <c r="C65" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D65" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E65" s="26" t="inlineStr">
@@ -5616,12 +6032,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I65" s="26" t="n">
-        <v>118674</v>
+      <c r="I65" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00140</t>
+        </is>
       </c>
       <c r="J65" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K65" s="26" t="inlineStr">
@@ -5655,12 +6073,12 @@
       </c>
       <c r="C66" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D66" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E66" s="26" t="inlineStr">
@@ -5683,12 +6101,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I66" s="26" t="n">
-        <v>118682</v>
+      <c r="I66" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00141</t>
+        </is>
       </c>
       <c r="J66" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K66" s="26" t="inlineStr">
@@ -5722,12 +6142,12 @@
       </c>
       <c r="C67" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D67" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E67" s="26" t="inlineStr">
@@ -5750,12 +6170,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I67" s="26" t="n">
-        <v>118543</v>
+      <c r="I67" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00127</t>
+        </is>
       </c>
       <c r="J67" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K67" s="26" t="inlineStr">
@@ -5789,12 +6211,12 @@
       </c>
       <c r="C68" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D68" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E68" s="26" t="inlineStr">
@@ -5817,12 +6239,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I68" s="26" t="n">
-        <v>118551</v>
+      <c r="I68" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00128</t>
+        </is>
       </c>
       <c r="J68" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K68" s="26" t="inlineStr">
@@ -5856,12 +6280,12 @@
       </c>
       <c r="C69" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D69" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E69" s="26" t="inlineStr">
@@ -5884,12 +6308,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I69" s="26" t="n">
-        <v>118560</v>
+      <c r="I69" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00129</t>
+        </is>
       </c>
       <c r="J69" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K69" s="26" t="inlineStr">
@@ -5923,12 +6349,12 @@
       </c>
       <c r="C70" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D70" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E70" s="26" t="inlineStr">
@@ -5951,12 +6377,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I70" s="26" t="n">
-        <v>118578</v>
+      <c r="I70" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00130</t>
+        </is>
       </c>
       <c r="J70" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K70" s="26" t="inlineStr">
@@ -5990,12 +6418,12 @@
       </c>
       <c r="C71" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D71" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E71" s="26" t="inlineStr">
@@ -6018,12 +6446,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I71" s="26" t="n">
-        <v>118586</v>
+      <c r="I71" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00131</t>
+        </is>
       </c>
       <c r="J71" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K71" s="26" t="inlineStr">
@@ -6057,12 +6487,12 @@
       </c>
       <c r="C72" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D72" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E72" s="26" t="inlineStr">
@@ -6085,12 +6515,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I72" s="26" t="n">
-        <v>118594</v>
+      <c r="I72" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00132</t>
+        </is>
       </c>
       <c r="J72" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K72" s="26" t="inlineStr">
@@ -6124,12 +6556,12 @@
       </c>
       <c r="C73" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D73" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E73" s="26" t="inlineStr">
@@ -6152,12 +6584,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I73" s="26" t="n">
-        <v>118261</v>
+      <c r="I73" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00099</t>
+        </is>
       </c>
       <c r="J73" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K73" s="26" t="inlineStr">
@@ -6191,12 +6625,12 @@
       </c>
       <c r="C74" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D74" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E74" s="26" t="inlineStr">
@@ -6219,12 +6653,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I74" s="26" t="n">
-        <v>118279</v>
+      <c r="I74" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00100</t>
+        </is>
       </c>
       <c r="J74" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K74" s="26" t="inlineStr">
@@ -6258,12 +6694,12 @@
       </c>
       <c r="C75" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D75" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E75" s="26" t="inlineStr">
@@ -6286,12 +6722,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I75" s="26" t="n">
-        <v>118501</v>
+      <c r="I75" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00123</t>
+        </is>
       </c>
       <c r="J75" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K75" s="26" t="inlineStr">
@@ -6325,12 +6763,12 @@
       </c>
       <c r="C76" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D76" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E76" s="26" t="inlineStr">
@@ -6353,12 +6791,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I76" s="26" t="n">
-        <v>118519</v>
+      <c r="I76" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00124</t>
+        </is>
       </c>
       <c r="J76" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K76" s="26" t="inlineStr">
@@ -6392,12 +6832,12 @@
       </c>
       <c r="C77" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D77" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E77" s="26" t="inlineStr">
@@ -6420,12 +6860,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I77" s="26" t="n">
-        <v>118527</v>
+      <c r="I77" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00125</t>
+        </is>
       </c>
       <c r="J77" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K77" s="26" t="inlineStr">
@@ -6459,12 +6901,12 @@
       </c>
       <c r="C78" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D78" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E78" s="26" t="inlineStr">
@@ -6487,12 +6929,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I78" s="26" t="n">
-        <v>118535</v>
+      <c r="I78" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00126</t>
+        </is>
       </c>
       <c r="J78" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K78" s="26" t="inlineStr">
@@ -6526,12 +6970,12 @@
       </c>
       <c r="C79" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D79" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E79" s="26" t="inlineStr">
@@ -6554,12 +6998,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I79" s="26" t="n">
-        <v>118471</v>
+      <c r="I79" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00120</t>
+        </is>
       </c>
       <c r="J79" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K79" s="26" t="inlineStr">
@@ -6593,12 +7039,12 @@
       </c>
       <c r="C80" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D80" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E80" s="26" t="inlineStr">
@@ -6621,12 +7067,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I80" s="26" t="n">
-        <v>106139</v>
+      <c r="I80" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00015</t>
+        </is>
       </c>
       <c r="J80" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K80" s="26" t="inlineStr">
@@ -6660,12 +7108,12 @@
       </c>
       <c r="C81" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D81" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E81" s="26" t="inlineStr">
@@ -6688,12 +7136,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I81" s="26" t="n">
-        <v>107959</v>
+      <c r="I81" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00016</t>
+        </is>
       </c>
       <c r="J81" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K81" s="26" t="inlineStr">
@@ -6727,12 +7177,12 @@
       </c>
       <c r="C82" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D82" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E82" s="26" t="inlineStr">
@@ -6755,12 +7205,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I82" s="26" t="n">
-        <v>110040</v>
+      <c r="I82" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00017</t>
+        </is>
       </c>
       <c r="J82" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K82" s="26" t="inlineStr">
@@ -6794,12 +7246,12 @@
       </c>
       <c r="C83" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D83" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E83" s="26" t="inlineStr">
@@ -6822,12 +7274,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I83" s="26" t="n">
-        <v>111886</v>
+      <c r="I83" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00020</t>
+        </is>
       </c>
       <c r="J83" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K83" s="26" t="inlineStr">
@@ -6861,12 +7315,12 @@
       </c>
       <c r="C84" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D84" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E84" s="26" t="inlineStr">
@@ -6889,12 +7343,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I84" s="26" t="n">
-        <v>116290</v>
+      <c r="I84" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00029</t>
+        </is>
       </c>
       <c r="J84" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K84" s="26" t="inlineStr">
@@ -6928,12 +7384,12 @@
       </c>
       <c r="C85" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D85" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E85" s="26" t="inlineStr">
@@ -6956,12 +7412,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I85" s="26" t="n">
-        <v>118113</v>
+      <c r="I85" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00086</t>
+        </is>
       </c>
       <c r="J85" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K85" s="26" t="inlineStr">
@@ -6995,12 +7453,12 @@
       </c>
       <c r="C86" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D86" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E86" s="26" t="inlineStr">
@@ -7023,12 +7481,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I86" s="26" t="n">
-        <v>118287</v>
+      <c r="I86" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00101</t>
+        </is>
       </c>
       <c r="J86" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K86" s="26" t="inlineStr">
@@ -7062,12 +7522,12 @@
       </c>
       <c r="C87" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D87" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E87" s="26" t="inlineStr">
@@ -7090,12 +7550,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I87" s="26" t="n">
-        <v>118367</v>
+      <c r="I87" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00109</t>
+        </is>
       </c>
       <c r="J87" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K87" s="26" t="inlineStr">
@@ -7129,12 +7591,12 @@
       </c>
       <c r="C88" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D88" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E88" s="26" t="inlineStr">
@@ -7157,12 +7619,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I88" s="26" t="n">
-        <v>118383</v>
+      <c r="I88" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00111</t>
+        </is>
       </c>
       <c r="J88" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K88" s="26" t="inlineStr">
@@ -7196,12 +7660,12 @@
       </c>
       <c r="C89" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D89" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E89" s="26" t="inlineStr">
@@ -7224,12 +7688,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I89" s="26" t="n">
-        <v>118404</v>
+      <c r="I89" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00113</t>
+        </is>
       </c>
       <c r="J89" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K89" s="26" t="inlineStr">
@@ -7263,12 +7729,12 @@
       </c>
       <c r="C90" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D90" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E90" s="26" t="inlineStr">
@@ -7291,12 +7757,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I90" s="26" t="n">
-        <v>118412</v>
+      <c r="I90" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00114</t>
+        </is>
       </c>
       <c r="J90" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K90" s="26" t="inlineStr">
@@ -7330,12 +7798,12 @@
       </c>
       <c r="C91" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D91" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E91" s="26" t="inlineStr">
@@ -7358,12 +7826,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I91" s="26" t="n">
-        <v>118463</v>
+      <c r="I91" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00119</t>
+        </is>
       </c>
       <c r="J91" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K91" s="26" t="inlineStr">
@@ -7397,12 +7867,12 @@
       </c>
       <c r="C92" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D92" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E92" s="26" t="inlineStr">
@@ -7425,12 +7895,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I92" s="26" t="n">
-        <v>118480</v>
+      <c r="I92" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00121</t>
+        </is>
       </c>
       <c r="J92" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K92" s="26" t="inlineStr">
@@ -7464,12 +7936,12 @@
       </c>
       <c r="C93" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D93" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E93" s="26" t="inlineStr">
@@ -7492,12 +7964,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I93" s="26" t="n">
-        <v>118498</v>
+      <c r="I93" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00122</t>
+        </is>
       </c>
       <c r="J93" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K93" s="26" t="inlineStr">
@@ -7531,12 +8005,12 @@
       </c>
       <c r="C94" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D94" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E94" s="26" t="inlineStr">
@@ -7559,12 +8033,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I94" s="26" t="n">
-        <v>117866</v>
+      <c r="I94" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00063</t>
+        </is>
       </c>
       <c r="J94" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K94" s="26" t="inlineStr">
@@ -7598,12 +8074,12 @@
       </c>
       <c r="C95" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D95" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E95" s="26" t="inlineStr">
@@ -7626,12 +8102,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I95" s="26" t="n">
-        <v>117962</v>
+      <c r="I95" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00071</t>
+        </is>
       </c>
       <c r="J95" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K95" s="26" t="inlineStr">
@@ -7665,12 +8143,12 @@
       </c>
       <c r="C96" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D96" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E96" s="26" t="inlineStr">
@@ -7693,12 +8171,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I96" s="26" t="n">
-        <v>117971</v>
+      <c r="I96" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00072</t>
+        </is>
       </c>
       <c r="J96" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K96" s="26" t="inlineStr">
@@ -7732,12 +8212,12 @@
       </c>
       <c r="C97" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D97" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E97" s="26" t="inlineStr">
@@ -7760,12 +8240,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I97" s="26" t="n">
-        <v>118375</v>
+      <c r="I97" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00110</t>
+        </is>
       </c>
       <c r="J97" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K97" s="26" t="inlineStr">
@@ -7799,12 +8281,12 @@
       </c>
       <c r="C98" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D98" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E98" s="26" t="inlineStr">
@@ -7827,12 +8309,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I98" s="26" t="n">
-        <v>118391</v>
+      <c r="I98" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00112</t>
+        </is>
       </c>
       <c r="J98" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K98" s="26" t="inlineStr">
@@ -7866,12 +8350,12 @@
       </c>
       <c r="C99" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D99" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E99" s="26" t="inlineStr">
@@ -7894,12 +8378,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I99" s="26" t="n">
-        <v>118421</v>
+      <c r="I99" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00115</t>
+        </is>
       </c>
       <c r="J99" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K99" s="26" t="inlineStr">
@@ -7933,12 +8419,12 @@
       </c>
       <c r="C100" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D100" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E100" s="26" t="inlineStr">
@@ -7961,12 +8447,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I100" s="26" t="n">
-        <v>118439</v>
+      <c r="I100" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00116</t>
+        </is>
       </c>
       <c r="J100" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K100" s="26" t="inlineStr">
@@ -8000,12 +8488,12 @@
       </c>
       <c r="C101" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D101" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E101" s="26" t="inlineStr">
@@ -8028,12 +8516,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I101" s="26" t="n">
-        <v>118447</v>
+      <c r="I101" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00117</t>
+        </is>
       </c>
       <c r="J101" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K101" s="26" t="inlineStr">
@@ -8067,12 +8557,12 @@
       </c>
       <c r="C102" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D102" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E102" s="26" t="inlineStr">
@@ -8095,12 +8585,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I102" s="26" t="n">
-        <v>118455</v>
+      <c r="I102" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00118</t>
+        </is>
       </c>
       <c r="J102" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K102" s="26" t="inlineStr">
@@ -8134,12 +8626,12 @@
       </c>
       <c r="C103" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D103" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E103" s="26" t="inlineStr">
@@ -8162,12 +8654,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I103" s="26" t="n">
-        <v>118308</v>
+      <c r="I103" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00103</t>
+        </is>
       </c>
       <c r="J103" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K103" s="26" t="inlineStr">
@@ -8201,12 +8695,12 @@
       </c>
       <c r="C104" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D104" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E104" s="26" t="inlineStr">
@@ -8229,12 +8723,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I104" s="26" t="n">
-        <v>118316</v>
+      <c r="I104" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00104</t>
+        </is>
       </c>
       <c r="J104" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K104" s="26" t="inlineStr">
@@ -8268,12 +8764,12 @@
       </c>
       <c r="C105" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D105" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E105" s="26" t="inlineStr">
@@ -8296,12 +8792,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I105" s="26" t="n">
-        <v>118324</v>
+      <c r="I105" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00105</t>
+        </is>
       </c>
       <c r="J105" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K105" s="26" t="inlineStr">
@@ -8335,12 +8833,12 @@
       </c>
       <c r="C106" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D106" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E106" s="26" t="inlineStr">
@@ -8363,12 +8861,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I106" s="26" t="n">
-        <v>118332</v>
+      <c r="I106" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00106</t>
+        </is>
       </c>
       <c r="J106" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K106" s="26" t="inlineStr">
@@ -8402,12 +8902,12 @@
       </c>
       <c r="C107" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D107" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E107" s="26" t="inlineStr">
@@ -8430,12 +8930,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I107" s="26" t="n">
-        <v>118341</v>
+      <c r="I107" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00107</t>
+        </is>
       </c>
       <c r="J107" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K107" s="26" t="inlineStr">
@@ -8469,12 +8971,12 @@
       </c>
       <c r="C108" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D108" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E108" s="26" t="inlineStr">
@@ -8497,12 +8999,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I108" s="26" t="n">
-        <v>118359</v>
+      <c r="I108" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00108</t>
+        </is>
       </c>
       <c r="J108" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K108" s="26" t="inlineStr">
@@ -8536,12 +9040,12 @@
       </c>
       <c r="C109" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D109" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E109" s="26" t="inlineStr">
@@ -8564,12 +9068,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I109" s="26" t="n">
-        <v>118041</v>
+      <c r="I109" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00079</t>
+        </is>
       </c>
       <c r="J109" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K109" s="26" t="inlineStr">
@@ -8603,12 +9109,12 @@
       </c>
       <c r="C110" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D110" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E110" s="26" t="inlineStr">
@@ -8631,12 +9137,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I110" s="26" t="n">
-        <v>118105</v>
+      <c r="I110" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00085</t>
+        </is>
       </c>
       <c r="J110" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K110" s="26" t="inlineStr">
@@ -8670,12 +9178,12 @@
       </c>
       <c r="C111" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D111" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E111" s="26" t="inlineStr">
@@ -8698,12 +9206,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I111" s="26" t="n">
-        <v>118199</v>
+      <c r="I111" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00092</t>
+        </is>
       </c>
       <c r="J111" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K111" s="26" t="inlineStr">
@@ -8737,12 +9247,12 @@
       </c>
       <c r="C112" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D112" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E112" s="26" t="inlineStr">
@@ -8765,12 +9275,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I112" s="26" t="n">
-        <v>118244</v>
+      <c r="I112" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00097</t>
+        </is>
       </c>
       <c r="J112" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K112" s="26" t="inlineStr">
@@ -8804,12 +9316,12 @@
       </c>
       <c r="C113" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D113" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E113" s="26" t="inlineStr">
@@ -8832,12 +9344,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I113" s="26" t="n">
-        <v>118252</v>
+      <c r="I113" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00098</t>
+        </is>
       </c>
       <c r="J113" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K113" s="26" t="inlineStr">
@@ -8871,12 +9385,12 @@
       </c>
       <c r="C114" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D114" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E114" s="26" t="inlineStr">
@@ -8899,12 +9413,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I114" s="26" t="n">
-        <v>118295</v>
+      <c r="I114" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00102</t>
+        </is>
       </c>
       <c r="J114" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K114" s="26" t="inlineStr">
@@ -8938,12 +9454,12 @@
       </c>
       <c r="C115" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D115" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E115" s="26" t="inlineStr">
@@ -8966,12 +9482,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I115" s="26" t="n">
-        <v>118156</v>
+      <c r="I115" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00090</t>
+        </is>
       </c>
       <c r="J115" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K115" s="26" t="inlineStr">
@@ -9005,12 +9523,12 @@
       </c>
       <c r="C116" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D116" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E116" s="26" t="inlineStr">
@@ -9033,12 +9551,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I116" s="26" t="n">
-        <v>118164</v>
+      <c r="I116" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00091</t>
+        </is>
       </c>
       <c r="J116" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K116" s="26" t="inlineStr">
@@ -9072,12 +9592,12 @@
       </c>
       <c r="C117" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D117" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E117" s="26" t="inlineStr">
@@ -9100,12 +9620,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I117" s="26" t="n">
-        <v>118201</v>
+      <c r="I117" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00093</t>
+        </is>
       </c>
       <c r="J117" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K117" s="26" t="inlineStr">
@@ -9139,12 +9661,12 @@
       </c>
       <c r="C118" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D118" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E118" s="26" t="inlineStr">
@@ -9167,12 +9689,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I118" s="26" t="n">
-        <v>118210</v>
+      <c r="I118" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00094</t>
+        </is>
       </c>
       <c r="J118" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K118" s="26" t="inlineStr">
@@ -9206,12 +9730,12 @@
       </c>
       <c r="C119" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D119" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E119" s="26" t="inlineStr">
@@ -9234,12 +9758,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I119" s="26" t="n">
-        <v>118228</v>
+      <c r="I119" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00095</t>
+        </is>
       </c>
       <c r="J119" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K119" s="26" t="inlineStr">
@@ -9273,12 +9799,12 @@
       </c>
       <c r="C120" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D120" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E120" s="26" t="inlineStr">
@@ -9301,12 +9827,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I120" s="26" t="n">
-        <v>118236</v>
+      <c r="I120" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00096</t>
+        </is>
       </c>
       <c r="J120" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K120" s="26" t="inlineStr">
@@ -9340,12 +9868,12 @@
       </c>
       <c r="C121" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D121" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E121" s="26" t="inlineStr">
@@ -9368,12 +9896,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I121" s="26" t="n">
-        <v>118076</v>
+      <c r="I121" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00082</t>
+        </is>
       </c>
       <c r="J121" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K121" s="26" t="inlineStr">
@@ -9407,12 +9937,12 @@
       </c>
       <c r="C122" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D122" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E122" s="26" t="inlineStr">
@@ -9435,12 +9965,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I122" s="26" t="n">
-        <v>118084</v>
+      <c r="I122" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00083</t>
+        </is>
       </c>
       <c r="J122" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K122" s="26" t="inlineStr">
@@ -9474,12 +10006,12 @@
       </c>
       <c r="C123" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D123" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E123" s="26" t="inlineStr">
@@ -9502,12 +10034,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I123" s="26" t="n">
-        <v>118092</v>
+      <c r="I123" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00084</t>
+        </is>
       </c>
       <c r="J123" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K123" s="26" t="inlineStr">
@@ -9541,12 +10075,12 @@
       </c>
       <c r="C124" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D124" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E124" s="26" t="inlineStr">
@@ -9569,12 +10103,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I124" s="26" t="n">
-        <v>118121</v>
+      <c r="I124" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00087</t>
+        </is>
       </c>
       <c r="J124" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K124" s="26" t="inlineStr">
@@ -9608,12 +10144,12 @@
       </c>
       <c r="C125" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D125" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E125" s="26" t="inlineStr">
@@ -9636,12 +10172,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I125" s="26" t="n">
-        <v>118130</v>
+      <c r="I125" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00088</t>
+        </is>
       </c>
       <c r="J125" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K125" s="26" t="inlineStr">
@@ -9675,12 +10213,12 @@
       </c>
       <c r="C126" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D126" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E126" s="26" t="inlineStr">
@@ -9703,12 +10241,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I126" s="26" t="n">
-        <v>118148</v>
+      <c r="I126" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00089</t>
+        </is>
       </c>
       <c r="J126" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K126" s="26" t="inlineStr">
@@ -9742,12 +10282,12 @@
       </c>
       <c r="C127" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D127" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E127" s="26" t="inlineStr">
@@ -9770,12 +10310,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I127" s="26" t="n">
-        <v>116126</v>
+      <c r="I127" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00026</t>
+        </is>
       </c>
       <c r="J127" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K127" s="26" t="inlineStr">
@@ -9809,12 +10351,12 @@
       </c>
       <c r="C128" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D128" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E128" s="26" t="inlineStr">
@@ -9837,12 +10379,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I128" s="26" t="n">
-        <v>116185</v>
+      <c r="I128" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00027</t>
+        </is>
       </c>
       <c r="J128" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K128" s="26" t="inlineStr">
@@ -9876,12 +10420,12 @@
       </c>
       <c r="C129" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D129" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E129" s="26" t="inlineStr">
@@ -9904,12 +10448,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I129" s="26" t="n">
-        <v>116193</v>
+      <c r="I129" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00028</t>
+        </is>
       </c>
       <c r="J129" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K129" s="26" t="inlineStr">
@@ -9943,12 +10489,12 @@
       </c>
       <c r="C130" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D130" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E130" s="26" t="inlineStr">
@@ -9971,12 +10517,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I130" s="26" t="n">
-        <v>118033</v>
+      <c r="I130" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00078</t>
+        </is>
       </c>
       <c r="J130" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K130" s="26" t="inlineStr">
@@ -10010,12 +10558,12 @@
       </c>
       <c r="C131" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D131" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E131" s="26" t="inlineStr">
@@ -10038,12 +10586,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I131" s="26" t="n">
-        <v>118050</v>
+      <c r="I131" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00080</t>
+        </is>
       </c>
       <c r="J131" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K131" s="26" t="inlineStr">
@@ -10077,12 +10627,12 @@
       </c>
       <c r="C132" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D132" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E132" s="26" t="inlineStr">
@@ -10105,12 +10655,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I132" s="26" t="n">
-        <v>118068</v>
+      <c r="I132" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00081</t>
+        </is>
       </c>
       <c r="J132" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K132" s="26" t="inlineStr">
@@ -10144,12 +10696,12 @@
       </c>
       <c r="C133" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D133" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E133" s="26" t="inlineStr">
@@ -10172,12 +10724,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I133" s="26" t="n">
-        <v>117680</v>
+      <c r="I133" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00047</t>
+        </is>
       </c>
       <c r="J133" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K133" s="26" t="inlineStr">
@@ -10211,12 +10765,12 @@
       </c>
       <c r="C134" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D134" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E134" s="26" t="inlineStr">
@@ -10239,12 +10793,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I134" s="26" t="n">
-        <v>117911</v>
+      <c r="I134" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00067</t>
+        </is>
       </c>
       <c r="J134" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K134" s="26" t="inlineStr">
@@ -10278,12 +10834,12 @@
       </c>
       <c r="C135" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D135" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E135" s="26" t="inlineStr">
@@ -10306,12 +10862,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I135" s="26" t="n">
-        <v>117989</v>
+      <c r="I135" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00073</t>
+        </is>
       </c>
       <c r="J135" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K135" s="26" t="inlineStr">
@@ -10345,12 +10903,12 @@
       </c>
       <c r="C136" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D136" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E136" s="26" t="inlineStr">
@@ -10373,12 +10931,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I136" s="26" t="n">
-        <v>110200</v>
+      <c r="I136" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00018</t>
+        </is>
       </c>
       <c r="J136" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K136" s="26" t="inlineStr">
@@ -10412,12 +10972,12 @@
       </c>
       <c r="C137" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D137" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E137" s="26" t="inlineStr">
@@ -10440,12 +11000,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I137" s="26" t="n">
-        <v>110218</v>
+      <c r="I137" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00019</t>
+        </is>
       </c>
       <c r="J137" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K137" s="26" t="inlineStr">
@@ -10479,12 +11041,12 @@
       </c>
       <c r="C138" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D138" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E138" s="26" t="inlineStr">
@@ -10507,12 +11069,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I138" s="26" t="n">
-        <v>116118</v>
+      <c r="I138" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00025</t>
+        </is>
       </c>
       <c r="J138" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K138" s="26" t="inlineStr">
@@ -10546,12 +11110,12 @@
       </c>
       <c r="C139" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D139" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E139" s="26" t="inlineStr">
@@ -10574,12 +11138,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I139" s="26" t="n">
-        <v>116370</v>
+      <c r="I139" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00030</t>
+        </is>
       </c>
       <c r="J139" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K139" s="26" t="inlineStr">
@@ -10613,12 +11179,12 @@
       </c>
       <c r="C140" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D140" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E140" s="26" t="inlineStr">
@@ -10641,12 +11207,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I140" s="26" t="n">
-        <v>116388</v>
+      <c r="I140" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00031</t>
+        </is>
       </c>
       <c r="J140" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K140" s="26" t="inlineStr">
@@ -10680,12 +11248,12 @@
       </c>
       <c r="C141" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D141" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E141" s="26" t="inlineStr">
@@ -10708,12 +11276,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I141" s="26" t="n">
-        <v>117591</v>
+      <c r="I141" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00038</t>
+        </is>
       </c>
       <c r="J141" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K141" s="26" t="inlineStr">
@@ -10747,12 +11317,12 @@
       </c>
       <c r="C142" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D142" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E142" s="26" t="inlineStr">
@@ -10775,12 +11345,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I142" s="26" t="n">
-        <v>117612</v>
+      <c r="I142" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00040</t>
+        </is>
       </c>
       <c r="J142" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K142" s="26" t="inlineStr">
@@ -10814,12 +11386,12 @@
       </c>
       <c r="C143" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D143" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E143" s="26" t="inlineStr">
@@ -10842,12 +11414,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I143" s="26" t="n">
-        <v>117621</v>
+      <c r="I143" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00041</t>
+        </is>
       </c>
       <c r="J143" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K143" s="26" t="inlineStr">
@@ -10881,12 +11455,12 @@
       </c>
       <c r="C144" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D144" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E144" s="26" t="inlineStr">
@@ -10909,12 +11483,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I144" s="26" t="n">
-        <v>117671</v>
+      <c r="I144" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00046</t>
+        </is>
       </c>
       <c r="J144" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K144" s="26" t="inlineStr">
@@ -10948,12 +11524,12 @@
       </c>
       <c r="C145" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D145" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E145" s="26" t="inlineStr">
@@ -10976,12 +11552,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I145" s="26" t="n">
-        <v>117938</v>
+      <c r="I145" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00069</t>
+        </is>
       </c>
       <c r="J145" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K145" s="26" t="inlineStr">
@@ -11015,12 +11593,12 @@
       </c>
       <c r="C146" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D146" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E146" s="26" t="inlineStr">
@@ -11043,12 +11621,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I146" s="26" t="n">
-        <v>117946</v>
+      <c r="I146" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00070</t>
+        </is>
       </c>
       <c r="J146" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K146" s="26" t="inlineStr">
@@ -11082,12 +11662,12 @@
       </c>
       <c r="C147" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D147" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E147" s="26" t="inlineStr">
@@ -11110,12 +11690,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I147" s="26" t="n">
-        <v>117997</v>
+      <c r="I147" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00074</t>
+        </is>
       </c>
       <c r="J147" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K147" s="26" t="inlineStr">
@@ -11149,12 +11731,12 @@
       </c>
       <c r="C148" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D148" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E148" s="26" t="inlineStr">
@@ -11177,12 +11759,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I148" s="26" t="n">
-        <v>118009</v>
+      <c r="I148" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00075</t>
+        </is>
       </c>
       <c r="J148" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K148" s="26" t="inlineStr">
@@ -11216,12 +11800,12 @@
       </c>
       <c r="C149" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D149" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E149" s="26" t="inlineStr">
@@ -11244,12 +11828,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I149" s="26" t="n">
-        <v>118017</v>
+      <c r="I149" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00076</t>
+        </is>
       </c>
       <c r="J149" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K149" s="26" t="inlineStr">
@@ -11283,12 +11869,12 @@
       </c>
       <c r="C150" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D150" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E150" s="26" t="inlineStr">
@@ -11311,12 +11897,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I150" s="26" t="n">
-        <v>118025</v>
+      <c r="I150" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00077</t>
+        </is>
       </c>
       <c r="J150" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K150" s="26" t="inlineStr">
@@ -11350,12 +11938,12 @@
       </c>
       <c r="C151" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D151" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E151" s="26" t="inlineStr">
@@ -11378,12 +11966,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I151" s="26" t="n">
-        <v>117840</v>
+      <c r="I151" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00061</t>
+        </is>
       </c>
       <c r="J151" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K151" s="26" t="inlineStr">
@@ -11417,12 +12007,12 @@
       </c>
       <c r="C152" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D152" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E152" s="26" t="inlineStr">
@@ -11445,12 +12035,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I152" s="26" t="n">
-        <v>117858</v>
+      <c r="I152" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00062</t>
+        </is>
       </c>
       <c r="J152" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K152" s="26" t="inlineStr">
@@ -11484,12 +12076,12 @@
       </c>
       <c r="C153" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D153" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E153" s="26" t="inlineStr">
@@ -11512,12 +12104,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I153" s="26" t="n">
-        <v>117874</v>
+      <c r="I153" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00064</t>
+        </is>
       </c>
       <c r="J153" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K153" s="26" t="inlineStr">
@@ -11551,12 +12145,12 @@
       </c>
       <c r="C154" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D154" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E154" s="26" t="inlineStr">
@@ -11579,12 +12173,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I154" s="26" t="n">
-        <v>117891</v>
+      <c r="I154" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00065</t>
+        </is>
       </c>
       <c r="J154" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K154" s="26" t="inlineStr">
@@ -11618,12 +12214,12 @@
       </c>
       <c r="C155" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D155" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E155" s="26" t="inlineStr">
@@ -11646,12 +12242,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I155" s="26" t="n">
-        <v>117903</v>
+      <c r="I155" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00066</t>
+        </is>
       </c>
       <c r="J155" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K155" s="26" t="inlineStr">
@@ -11685,12 +12283,12 @@
       </c>
       <c r="C156" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D156" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E156" s="26" t="inlineStr">
@@ -11713,12 +12311,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I156" s="26" t="n">
-        <v>117920</v>
+      <c r="I156" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00068</t>
+        </is>
       </c>
       <c r="J156" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K156" s="26" t="inlineStr">
@@ -11752,12 +12352,12 @@
       </c>
       <c r="C157" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D157" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E157" s="26" t="inlineStr">
@@ -11780,12 +12380,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I157" s="26" t="n">
-        <v>117760</v>
+      <c r="I157" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00055</t>
+        </is>
       </c>
       <c r="J157" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K157" s="26" t="inlineStr">
@@ -11819,12 +12421,12 @@
       </c>
       <c r="C158" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D158" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E158" s="26" t="inlineStr">
@@ -11847,12 +12449,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I158" s="26" t="n">
-        <v>117778</v>
+      <c r="I158" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00056</t>
+        </is>
       </c>
       <c r="J158" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K158" s="26" t="inlineStr">
@@ -11886,12 +12490,12 @@
       </c>
       <c r="C159" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D159" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E159" s="26" t="inlineStr">
@@ -11914,12 +12518,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I159" s="26" t="n">
-        <v>117786</v>
+      <c r="I159" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00057</t>
+        </is>
       </c>
       <c r="J159" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K159" s="26" t="inlineStr">
@@ -11953,12 +12559,12 @@
       </c>
       <c r="C160" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D160" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E160" s="26" t="inlineStr">
@@ -11981,12 +12587,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I160" s="26" t="n">
-        <v>117794</v>
+      <c r="I160" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00058</t>
+        </is>
       </c>
       <c r="J160" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K160" s="26" t="inlineStr">
@@ -12020,12 +12628,12 @@
       </c>
       <c r="C161" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D161" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E161" s="26" t="inlineStr">
@@ -12048,12 +12656,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I161" s="26" t="n">
-        <v>117815</v>
+      <c r="I161" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00059</t>
+        </is>
       </c>
       <c r="J161" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K161" s="26" t="inlineStr">
@@ -12087,12 +12697,12 @@
       </c>
       <c r="C162" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D162" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E162" s="26" t="inlineStr">
@@ -12115,12 +12725,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I162" s="26" t="n">
-        <v>117823</v>
+      <c r="I162" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00060</t>
+        </is>
       </c>
       <c r="J162" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K162" s="26" t="inlineStr">
@@ -12154,12 +12766,12 @@
       </c>
       <c r="C163" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D163" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E163" s="26" t="inlineStr">
@@ -12182,12 +12794,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I163" s="26" t="n">
-        <v>117701</v>
+      <c r="I163" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00049</t>
+        </is>
       </c>
       <c r="J163" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K163" s="26" t="inlineStr">
@@ -12221,12 +12835,12 @@
       </c>
       <c r="C164" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D164" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E164" s="26" t="inlineStr">
@@ -12249,12 +12863,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I164" s="26" t="n">
-        <v>117719</v>
+      <c r="I164" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00050</t>
+        </is>
       </c>
       <c r="J164" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K164" s="26" t="inlineStr">
@@ -12288,12 +12904,12 @@
       </c>
       <c r="C165" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D165" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E165" s="26" t="inlineStr">
@@ -12316,12 +12932,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I165" s="26" t="n">
-        <v>117727</v>
+      <c r="I165" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00051</t>
+        </is>
       </c>
       <c r="J165" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K165" s="26" t="inlineStr">
@@ -12355,12 +12973,12 @@
       </c>
       <c r="C166" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D166" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E166" s="26" t="inlineStr">
@@ -12383,12 +13001,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I166" s="26" t="n">
-        <v>117735</v>
+      <c r="I166" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00052</t>
+        </is>
       </c>
       <c r="J166" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K166" s="26" t="inlineStr">
@@ -12422,12 +13042,12 @@
       </c>
       <c r="C167" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D167" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E167" s="26" t="inlineStr">
@@ -12450,12 +13070,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I167" s="26" t="n">
-        <v>117743</v>
+      <c r="I167" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00053</t>
+        </is>
       </c>
       <c r="J167" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K167" s="26" t="inlineStr">
@@ -12489,12 +13111,12 @@
       </c>
       <c r="C168" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D168" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E168" s="26" t="inlineStr">
@@ -12517,12 +13139,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I168" s="26" t="n">
-        <v>117751</v>
+      <c r="I168" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00054</t>
+        </is>
       </c>
       <c r="J168" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K168" s="26" t="inlineStr">
@@ -12556,12 +13180,12 @@
       </c>
       <c r="C169" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D169" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E169" s="26" t="inlineStr">
@@ -12584,12 +13208,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I169" s="26" t="n">
-        <v>117604</v>
+      <c r="I169" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00039</t>
+        </is>
       </c>
       <c r="J169" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K169" s="26" t="inlineStr">
@@ -12623,12 +13249,12 @@
       </c>
       <c r="C170" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D170" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E170" s="26" t="inlineStr">
@@ -12651,12 +13277,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I170" s="26" t="n">
-        <v>117639</v>
+      <c r="I170" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00042</t>
+        </is>
       </c>
       <c r="J170" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K170" s="26" t="inlineStr">
@@ -12690,12 +13318,12 @@
       </c>
       <c r="C171" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D171" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E171" s="26" t="inlineStr">
@@ -12718,12 +13346,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I171" s="26" t="n">
-        <v>117647</v>
+      <c r="I171" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00043</t>
+        </is>
       </c>
       <c r="J171" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K171" s="26" t="inlineStr">
@@ -12757,12 +13387,12 @@
       </c>
       <c r="C172" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D172" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E172" s="26" t="inlineStr">
@@ -12785,12 +13415,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I172" s="26" t="n">
-        <v>117655</v>
+      <c r="I172" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00044</t>
+        </is>
       </c>
       <c r="J172" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K172" s="26" t="inlineStr">
@@ -12824,12 +13456,12 @@
       </c>
       <c r="C173" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D173" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E173" s="26" t="inlineStr">
@@ -12852,12 +13484,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I173" s="26" t="n">
-        <v>117663</v>
+      <c r="I173" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00045</t>
+        </is>
       </c>
       <c r="J173" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K173" s="26" t="inlineStr">
@@ -12891,12 +13525,12 @@
       </c>
       <c r="C174" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D174" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E174" s="26" t="inlineStr">
@@ -12919,12 +13553,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I174" s="26" t="n">
-        <v>117698</v>
+      <c r="I174" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00048</t>
+        </is>
       </c>
       <c r="J174" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K174" s="26" t="inlineStr">
@@ -12958,12 +13594,12 @@
       </c>
       <c r="C175" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D175" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E175" s="26" t="inlineStr">
@@ -12986,12 +13622,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I175" s="26" t="n">
-        <v>117348</v>
+      <c r="I175" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00032</t>
+        </is>
       </c>
       <c r="J175" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K175" s="26" t="inlineStr">
@@ -13025,12 +13663,12 @@
       </c>
       <c r="C176" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D176" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E176" s="26" t="inlineStr">
@@ -13053,12 +13691,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I176" s="26" t="n">
-        <v>117495</v>
+      <c r="I176" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00033</t>
+        </is>
       </c>
       <c r="J176" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K176" s="26" t="inlineStr">
@@ -13092,12 +13732,12 @@
       </c>
       <c r="C177" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D177" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E177" s="26" t="inlineStr">
@@ -13120,12 +13760,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I177" s="26" t="n">
-        <v>117532</v>
+      <c r="I177" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00034</t>
+        </is>
       </c>
       <c r="J177" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K177" s="26" t="inlineStr">
@@ -13159,12 +13801,12 @@
       </c>
       <c r="C178" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D178" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E178" s="26" t="inlineStr">
@@ -13187,12 +13829,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I178" s="26" t="n">
-        <v>117567</v>
+      <c r="I178" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00035</t>
+        </is>
       </c>
       <c r="J178" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K178" s="26" t="inlineStr">
@@ -13226,12 +13870,12 @@
       </c>
       <c r="C179" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D179" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E179" s="26" t="inlineStr">
@@ -13254,12 +13898,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I179" s="26" t="n">
-        <v>117575</v>
+      <c r="I179" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00036</t>
+        </is>
       </c>
       <c r="J179" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K179" s="26" t="inlineStr">
@@ -13293,12 +13939,12 @@
       </c>
       <c r="C180" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D180" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E180" s="26" t="inlineStr">
@@ -13321,12 +13967,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I180" s="26" t="n">
-        <v>117583</v>
+      <c r="I180" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00037</t>
+        </is>
       </c>
       <c r="J180" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K180" s="26" t="inlineStr">
@@ -13360,12 +14008,12 @@
       </c>
       <c r="C181" s="25" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D181" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E181" s="25" t="inlineStr">
@@ -13388,12 +14036,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I181" s="25" t="n">
-        <v>116812</v>
+      <c r="I181" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00012</t>
+        </is>
       </c>
       <c r="J181" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K181" s="25" t="inlineStr">
@@ -13427,12 +14077,12 @@
       </c>
       <c r="C182" s="25" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D182" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">73040.1421                   </t>
+          <t xml:space="preserve">80040.3810                   </t>
         </is>
       </c>
       <c r="E182" s="25" t="inlineStr">
@@ -13455,12 +14105,14 @@
           <t>SO</t>
         </is>
       </c>
-      <c r="I182" s="25" t="n">
-        <v>115545</v>
+      <c r="I182" s="25" t="inlineStr">
+        <is>
+          <t>DOC-00014</t>
+        </is>
       </c>
       <c r="J182" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73040</t>
+          <t xml:space="preserve">       80040</t>
         </is>
       </c>
       <c r="K182" s="25" t="inlineStr">
@@ -13494,12 +14146,12 @@
       </c>
       <c r="C183" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D183" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E183" s="26" t="inlineStr">
@@ -13522,12 +14174,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I183" s="26" t="n">
-        <v>116003</v>
+      <c r="I183" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00021</t>
+        </is>
       </c>
       <c r="J183" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K183" s="26" t="inlineStr">
@@ -13561,12 +14215,12 @@
       </c>
       <c r="C184" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D184" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E184" s="26" t="inlineStr">
@@ -13589,12 +14243,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I184" s="26" t="n">
-        <v>116011</v>
+      <c r="I184" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00022</t>
+        </is>
       </c>
       <c r="J184" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K184" s="26" t="inlineStr">
@@ -13628,12 +14284,12 @@
       </c>
       <c r="C185" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D185" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E185" s="26" t="inlineStr">
@@ -13656,12 +14312,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I185" s="26" t="n">
-        <v>116020</v>
+      <c r="I185" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00023</t>
+        </is>
       </c>
       <c r="J185" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K185" s="26" t="inlineStr">
@@ -13695,12 +14353,12 @@
       </c>
       <c r="C186" s="26" t="inlineStr">
         <is>
-          <t>00073</t>
+          <t>00080</t>
         </is>
       </c>
       <c r="D186" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">73010.1421                   </t>
+          <t xml:space="preserve">80010.3810                   </t>
         </is>
       </c>
       <c r="E186" s="26" t="inlineStr">
@@ -13723,12 +14381,14 @@
           <t>SI</t>
         </is>
       </c>
-      <c r="I186" s="26" t="n">
-        <v>116038</v>
+      <c r="I186" s="26" t="inlineStr">
+        <is>
+          <t>DOC-00024</t>
+        </is>
       </c>
       <c r="J186" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">       73010</t>
+          <t xml:space="preserve">       80010</t>
         </is>
       </c>
       <c r="K186" s="26" t="inlineStr">
